--- a/data/availability/projects/hyde-park-developments/hyde-park-new-cairo.xlsx
+++ b/data/availability/projects/hyde-park-developments/hyde-park-new-cairo.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory export for hyde-park-new-cairo</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -587,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +847,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +897,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +947,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +997,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1047,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1087,7 +1097,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1137,7 +1147,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1187,7 +1197,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1204,7 +1214,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1237,7 +1247,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1287,7 +1297,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1337,7 +1347,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1387,7 +1397,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1437,7 +1447,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1487,7 +1497,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1537,7 +1547,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1587,7 +1597,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1724,7 +1734,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1785,7 +1795,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1846,7 +1856,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1907,7 +1917,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1968,7 +1978,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -2029,7 +2039,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2090,7 +2100,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2151,7 +2161,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2212,7 +2222,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2273,7 +2283,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2334,7 +2344,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2395,7 +2405,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2456,7 +2466,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2517,7 +2527,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2578,7 +2588,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2639,7 +2649,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2700,7 +2710,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2761,7 +2771,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2822,7 +2832,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2883,7 +2893,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2944,7 +2954,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3005,7 +3015,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3066,7 +3076,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3112,7 +3122,6 @@
       <c r="G25" t="n">
         <v>108</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3123,7 +3132,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3169,7 +3178,6 @@
       <c r="G26" t="n">
         <v>108</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3180,7 +3188,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3226,7 +3234,6 @@
       <c r="G27" t="n">
         <v>108</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3237,7 +3244,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3283,7 +3290,6 @@
       <c r="G28" t="n">
         <v>100</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3294,7 +3300,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3340,7 +3346,6 @@
       <c r="G29" t="n">
         <v>108</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3351,7 +3356,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3397,7 +3402,6 @@
       <c r="G30" t="n">
         <v>108</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3408,7 +3412,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3454,7 +3458,6 @@
       <c r="G31" t="n">
         <v>108</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3465,7 +3468,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3511,7 +3514,6 @@
       <c r="G32" t="n">
         <v>100</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3522,7 +3524,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3568,7 +3570,6 @@
       <c r="G33" t="n">
         <v>108.4491194</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3579,7 +3580,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3625,7 +3626,6 @@
       <c r="G34" t="n">
         <v>68.20878826000001</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3682,7 +3682,6 @@
       <c r="G35" t="n">
         <v>68.20878826000001</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3693,7 +3692,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3739,7 +3738,6 @@
       <c r="G36" t="n">
         <v>68.20878826000001</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3750,7 +3748,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3796,7 +3794,6 @@
       <c r="G37" t="n">
         <v>148.4040581</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3807,7 +3804,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3853,7 +3850,6 @@
       <c r="G38" t="n">
         <v>68.20878826000001</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3864,7 +3860,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3910,7 +3906,6 @@
       <c r="G39" t="n">
         <v>148.4040581</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3921,7 +3916,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3967,7 +3962,6 @@
       <c r="G40" t="n">
         <v>108.4491194</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -3978,7 +3972,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4024,7 +4018,6 @@
       <c r="G41" t="n">
         <v>68.20878826000001</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4035,7 +4028,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4081,7 +4074,6 @@
       <c r="G42" t="n">
         <v>108.4491194</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4092,7 +4084,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4138,7 +4130,6 @@
       <c r="G43" t="n">
         <v>148.4040581</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4149,7 +4140,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4195,7 +4186,6 @@
       <c r="G44" t="n">
         <v>68.20878826000001</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4206,7 +4196,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4252,7 +4242,6 @@
       <c r="G45" t="n">
         <v>68.20878826000001</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4263,7 +4252,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4309,7 +4298,6 @@
       <c r="G46" t="n">
         <v>68.20878826000001</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4320,7 +4308,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4366,7 +4354,6 @@
       <c r="G47" t="n">
         <v>131</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4377,7 +4364,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4423,7 +4410,6 @@
       <c r="G48" t="n">
         <v>99.52941176</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4434,7 +4420,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4480,7 +4466,6 @@
       <c r="G49" t="n">
         <v>107.9341176</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4491,7 +4476,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4537,7 +4522,6 @@
       <c r="G50" t="n">
         <v>107.9341176</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4548,7 +4532,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4594,7 +4578,6 @@
       <c r="G51" t="n">
         <v>108.4491194</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4605,7 +4588,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4651,7 +4634,6 @@
       <c r="G52" t="n">
         <v>68.20878826000001</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4662,7 +4644,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4708,7 +4690,6 @@
       <c r="G53" t="n">
         <v>108.4491194</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4719,7 +4700,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4765,7 +4746,6 @@
       <c r="G54" t="n">
         <v>108.277884</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4776,7 +4756,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4822,7 +4802,6 @@
       <c r="G55" t="n">
         <v>108.4491194</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4833,7 +4812,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4879,7 +4858,6 @@
       <c r="G56" t="n">
         <v>108</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4890,7 +4868,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4936,7 +4914,6 @@
       <c r="G57" t="n">
         <v>99.52941176</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -4947,7 +4924,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4993,7 +4970,6 @@
       <c r="G58" t="n">
         <v>107.9341176</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5004,7 +4980,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5050,7 +5026,6 @@
       <c r="G59" t="n">
         <v>107.9341176</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5061,7 +5036,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5107,7 +5082,6 @@
       <c r="G60" t="n">
         <v>107.9341176</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5118,7 +5092,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5164,7 +5138,6 @@
       <c r="G61" t="n">
         <v>51</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5175,7 +5148,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5221,7 +5194,6 @@
       <c r="G62" t="n">
         <v>78</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5232,7 +5204,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5278,7 +5250,6 @@
       <c r="G63" t="n">
         <v>81</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5289,7 +5260,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5335,7 +5306,6 @@
       <c r="G64" t="n">
         <v>79</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5346,7 +5316,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5392,7 +5362,6 @@
       <c r="G65" t="n">
         <v>51</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5403,7 +5372,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5449,7 +5418,6 @@
       <c r="G66" t="n">
         <v>50</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5460,7 +5428,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5506,7 +5474,6 @@
       <c r="G67" t="n">
         <v>88</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5517,7 +5484,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5563,7 +5530,6 @@
       <c r="G68" t="n">
         <v>90</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5574,7 +5540,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5620,7 +5586,6 @@
       <c r="G69" t="n">
         <v>78</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5631,7 +5596,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5677,7 +5642,6 @@
       <c r="G70" t="n">
         <v>80.5</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5688,7 +5652,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5734,7 +5698,6 @@
       <c r="G71" t="n">
         <v>74.5</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5745,7 +5708,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5791,7 +5754,6 @@
       <c r="G72" t="n">
         <v>50</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5802,7 +5764,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5848,7 +5810,6 @@
       <c r="G73" t="n">
         <v>49</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5859,7 +5820,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5905,7 +5866,6 @@
       <c r="G74" t="n">
         <v>83</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5916,7 +5876,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5962,7 +5922,6 @@
       <c r="G75" t="n">
         <v>89</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -5973,7 +5932,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6019,7 +5978,6 @@
       <c r="G76" t="n">
         <v>78</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6030,7 +5988,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6076,7 +6034,6 @@
       <c r="G77" t="n">
         <v>80.5</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6087,7 +6044,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6133,7 +6090,6 @@
       <c r="G78" t="n">
         <v>116.1478755</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6144,7 +6100,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6190,7 +6146,6 @@
       <c r="G79" t="n">
         <v>160.6840028</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6201,7 +6156,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6247,7 +6202,6 @@
       <c r="G80" t="n">
         <v>116.2267803</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6258,7 +6212,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6304,7 +6258,6 @@
       <c r="G81" t="n">
         <v>78.28484038000001</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6315,7 +6268,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6361,7 +6314,6 @@
       <c r="G82" t="n">
         <v>78.28484038000001</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6372,7 +6324,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6418,7 +6370,6 @@
       <c r="G83" t="n">
         <v>116.1478755</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6429,7 +6380,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6475,7 +6426,6 @@
       <c r="G84" t="n">
         <v>116.2267803</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6486,7 +6436,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6532,7 +6482,6 @@
       <c r="G85" t="n">
         <v>87.40398162</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6543,7 +6492,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6589,7 +6538,6 @@
       <c r="G86" t="n">
         <v>78.28484038000001</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6600,7 +6548,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6646,7 +6594,6 @@
       <c r="G87" t="n">
         <v>116.2267803</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6657,7 +6604,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6718,7 +6665,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6764,7 +6711,6 @@
       <c r="G89" t="n">
         <v>78.28484038000001</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6775,7 +6721,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6821,7 +6767,6 @@
       <c r="G90" t="n">
         <v>78.28484038000001</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6832,7 +6777,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6878,7 +6823,6 @@
       <c r="G91" t="n">
         <v>78.28484038000001</v>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6889,7 +6833,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6935,7 +6879,6 @@
       <c r="G92" t="n">
         <v>116.1478755</v>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -6946,7 +6889,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6992,7 +6935,6 @@
       <c r="G93" t="n">
         <v>160.6840028</v>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7003,7 +6945,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7049,7 +6991,6 @@
       <c r="G94" t="n">
         <v>116.2267803</v>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7060,7 +7001,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7106,7 +7047,6 @@
       <c r="G95" t="n">
         <v>116.1478755</v>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7117,7 +7057,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7163,7 +7103,6 @@
       <c r="G96" t="n">
         <v>78.28484038000001</v>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7174,7 +7113,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7220,7 +7159,6 @@
       <c r="G97" t="n">
         <v>116.2267803</v>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7231,7 +7169,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7277,7 +7215,6 @@
       <c r="G98" t="n">
         <v>116.2267803</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7288,7 +7225,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7334,7 +7271,6 @@
       <c r="G99" t="n">
         <v>87.40398162</v>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7345,7 +7281,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7367,7 +7303,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7391,7 +7327,6 @@
       <c r="G100" t="n">
         <v>110</v>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7402,7 +7337,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7424,7 +7359,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7448,7 +7383,6 @@
       <c r="G101" t="n">
         <v>89</v>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7459,7 +7393,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7481,7 +7415,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7505,7 +7439,6 @@
       <c r="G102" t="n">
         <v>75</v>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7516,7 +7449,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7538,7 +7471,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7562,7 +7495,6 @@
       <c r="G103" t="n">
         <v>110</v>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7573,7 +7505,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7595,7 +7527,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7619,7 +7551,6 @@
       <c r="G104" t="n">
         <v>110</v>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7630,7 +7561,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7652,7 +7583,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7676,7 +7607,6 @@
       <c r="G105" t="n">
         <v>80</v>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7687,7 +7617,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7709,7 +7639,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7733,7 +7663,6 @@
       <c r="G106" t="n">
         <v>70</v>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7744,7 +7673,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7766,7 +7695,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7790,7 +7719,6 @@
       <c r="G107" t="n">
         <v>110</v>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7801,7 +7729,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7823,7 +7751,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7847,7 +7775,6 @@
       <c r="G108" t="n">
         <v>105</v>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7858,7 +7785,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7880,7 +7807,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7904,7 +7831,6 @@
       <c r="G109" t="n">
         <v>75</v>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7915,7 +7841,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7937,7 +7863,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7961,7 +7887,6 @@
       <c r="G110" t="n">
         <v>75</v>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -7972,7 +7897,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7994,7 +7919,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -8018,7 +7943,6 @@
       <c r="G111" t="n">
         <v>80</v>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8029,7 +7953,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8051,7 +7975,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -8075,7 +7999,6 @@
       <c r="G112" t="n">
         <v>84</v>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8086,7 +8009,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8108,7 +8031,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -8132,7 +8055,6 @@
       <c r="G113" t="n">
         <v>50</v>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8143,7 +8065,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8165,7 +8087,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -8189,7 +8111,6 @@
       <c r="G114" t="n">
         <v>65</v>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8200,7 +8121,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8222,7 +8143,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -8246,7 +8167,6 @@
       <c r="G115" t="n">
         <v>65</v>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8257,7 +8177,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8279,7 +8199,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -8303,7 +8223,6 @@
       <c r="G116" t="n">
         <v>75</v>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8314,7 +8233,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8360,7 +8279,6 @@
       <c r="G117" t="n">
         <v>120</v>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8371,7 +8289,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8417,7 +8335,6 @@
       <c r="G118" t="n">
         <v>120</v>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8428,7 +8345,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8474,7 +8391,6 @@
       <c r="G119" t="n">
         <v>75</v>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8485,7 +8401,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8531,7 +8447,6 @@
       <c r="G120" t="n">
         <v>113.3785096</v>
       </c>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8542,7 +8457,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8588,7 +8503,6 @@
       <c r="G121" t="n">
         <v>118.343149</v>
       </c>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8599,7 +8513,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8645,7 +8559,6 @@
       <c r="G122" t="n">
         <v>120</v>
       </c>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8656,7 +8569,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8702,7 +8615,6 @@
       <c r="G123" t="n">
         <v>115.3363569</v>
       </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8713,7 +8625,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8759,7 +8671,6 @@
       <c r="G124" t="n">
         <v>122.8766917</v>
       </c>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8770,7 +8681,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8816,7 +8727,6 @@
       <c r="G125" t="n">
         <v>123</v>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8827,7 +8737,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8873,7 +8783,6 @@
       <c r="G126" t="n">
         <v>82</v>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8884,7 +8793,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8930,7 +8839,6 @@
       <c r="G127" t="n">
         <v>125.4352737</v>
       </c>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8941,7 +8849,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8987,7 +8895,6 @@
       <c r="G128" t="n">
         <v>122.8766917</v>
       </c>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -8998,7 +8905,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9044,7 +8951,6 @@
       <c r="G129" t="n">
         <v>88</v>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -9055,7 +8961,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9101,7 +9007,6 @@
       <c r="G130" t="n">
         <v>125.5541697</v>
       </c>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -9112,7 +9017,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9173,7 +9078,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9234,7 +9139,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9295,7 +9200,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9356,7 +9261,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -9417,7 +9322,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -9478,7 +9383,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -9539,7 +9444,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9561,7 +9466,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9585,7 +9490,6 @@
       <c r="G138" t="n">
         <v>144</v>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -9596,7 +9500,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9618,7 +9522,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9642,7 +9546,6 @@
       <c r="G139" t="n">
         <v>144</v>
       </c>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>Landscape &amp; Lagoon</t>
@@ -9653,7 +9556,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2027-2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
